--- a/src/test/resources/TEST_DATA/MyAccountPageData.xlsx
+++ b/src/test/resources/TEST_DATA/MyAccountPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="SADetailedViewData" sheetId="1" state="visible" r:id="rId1"/>
@@ -57,13 +57,13 @@
     <t xml:space="preserve">LKR 0.00</t>
   </si>
   <si>
-    <t xml:space="preserve">LKR 27,000.00</t>
+    <t xml:space="preserve">LKR 77,000.00</t>
   </si>
   <si>
     <t>21-07-2024</t>
   </si>
   <si>
-    <t xml:space="preserve">LKR 2,116.00</t>
+    <t xml:space="preserve">LKR 104,181.00</t>
   </si>
   <si>
     <t>123.00</t>
@@ -84,19 +84,19 @@
     <t>openedOn</t>
   </si>
   <si>
-    <t>002550040541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LKR 150,000.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LKR 230,870.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LKR 53,776.17</t>
-  </si>
-  <si>
-    <t>18-02-2020</t>
+    <t>003950009402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LKR 100,000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LKR 5,281.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LKR 91,854.45</t>
+  </si>
+  <si>
+    <t>07-11-2005</t>
   </si>
   <si>
     <t>month</t>
@@ -163,8 +163,9 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -675,12 +676,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" style="1" width="14.57421875"/>
     <col bestFit="1" min="2" max="2" style="1" width="14.140625"/>
     <col bestFit="1" min="3" max="3" style="1" width="14.7109375"/>
-    <col bestFit="1" min="4" max="4" style="1" width="10.7109375"/>
+    <col customWidth="1" min="4" max="4" style="1" width="30.140625"/>
     <col bestFit="1" min="5" max="5" style="1" width="12.8515625"/>
     <col bestFit="1" min="6" max="6" style="1" width="14.140625"/>
     <col bestFit="1" min="7" max="7" style="1" width="11.140625"/>
@@ -724,22 +725,22 @@
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -756,16 +757,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="5" style="1" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="1" width="24.140625"/>
+    <col customWidth="1" min="2" max="2" style="1" width="23.421875"/>
+    <col customWidth="1" min="3" max="3" style="1" width="21.140625"/>
+    <col customWidth="1" min="4" max="4" style="1" width="26.421875"/>
+    <col customWidth="1" min="5" max="5" style="1" width="31.00390625"/>
     <col bestFit="1" min="6" max="6" style="1" width="14.140625"/>
     <col bestFit="1" min="7" max="7" style="1" width="9.8515625"/>
     <col min="8" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -831,7 +836,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -852,7 +857,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
